--- a/Versão5/TUBO/Ontologia_TUBOS.xlsx
+++ b/Versão5/TUBO/Ontologia_TUBOS.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Construtor_Onto\TUBO\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7C7C7069-C31C-4CE3-AA3E-209ED03E4DD9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4C1733EE-551D-4A9F-B078-18E14C6B5D7C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-103" yWindow="-103" windowWidth="22149" windowHeight="13200" tabRatio="520" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4489" uniqueCount="843">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4611" uniqueCount="845">
   <si>
     <t>EquivalentTo: 
 Raiz
@@ -2601,6 +2601,12 @@
   </si>
   <si>
     <t>quem.fabricou</t>
+  </si>
+  <si>
+    <t>código.abnt</t>
+  </si>
+  <si>
+    <t>"[ 0M.20.20.01.07.03 ]"</t>
   </si>
 </sst>
 </file>
@@ -4014,7 +4020,7 @@
       </c>
       <c r="B18" s="37">
         <f ca="1">NOW()</f>
-        <v>46213.789097106484</v>
+        <v>46214.396773611108</v>
       </c>
       <c r="C18" s="68" t="s">
         <v>497</v>
@@ -15824,17 +15830,17 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{38CB0525-EDFB-44CB-9009-6752AEDD7340}">
   <sheetPr codeName="Planilha4"/>
-  <dimension ref="A1:AO61"/>
+  <dimension ref="A1:AQ61"/>
   <sheetFormatPr defaultColWidth="5.3046875" defaultRowHeight="7.5" customHeight="1" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="1" max="1" width="2.3046875" style="43" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="15.69140625" style="43" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="11.69140625" style="43" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="9.3046875" style="54" customWidth="1"/>
     <col min="4" max="4" width="7.69140625" style="43" customWidth="1"/>
-    <col min="5" max="5" width="15.69140625" style="43" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="11.69140625" style="43" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="4.3046875" style="54" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="5.84375" style="54" customWidth="1"/>
-    <col min="8" max="8" width="5.69140625" style="54" customWidth="1"/>
+    <col min="7" max="7" width="4.4609375" style="54" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="3.4609375" style="54" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="14" style="54" customWidth="1"/>
     <col min="10" max="10" width="3.15234375" style="54" customWidth="1"/>
     <col min="11" max="11" width="3.69140625" style="54" customWidth="1"/>
@@ -15867,11 +15873,13 @@
     <col min="38" max="38" width="7" style="43" customWidth="1"/>
     <col min="39" max="39" width="10.15234375" style="43" bestFit="1" customWidth="1"/>
     <col min="40" max="40" width="5.3046875" style="43"/>
-    <col min="41" max="41" width="14.3046875" style="43" bestFit="1" customWidth="1"/>
-    <col min="42" max="16384" width="5.3046875" style="43"/>
+    <col min="41" max="41" width="8" style="43" customWidth="1"/>
+    <col min="42" max="42" width="5.3046875" style="43"/>
+    <col min="43" max="43" width="9.53515625" style="43" bestFit="1" customWidth="1"/>
+    <col min="44" max="16384" width="5.3046875" style="43"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:41" ht="25.5" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:43" ht="25.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A1" s="38" t="s">
         <v>10</v>
       </c>
@@ -15991,8 +15999,14 @@
       <c r="AO1" s="42" t="s">
         <v>78</v>
       </c>
+      <c r="AP1" s="40" t="s">
+        <v>76</v>
+      </c>
+      <c r="AQ1" s="42" t="s">
+        <v>78</v>
+      </c>
     </row>
-    <row r="2" spans="1:41" ht="7.5" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="2" spans="1:43" ht="7.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A2" s="16">
         <v>2</v>
       </c>
@@ -16116,8 +16130,14 @@
       <c r="AO2" s="59" t="s">
         <v>9</v>
       </c>
+      <c r="AP2" s="62" t="s">
+        <v>9</v>
+      </c>
+      <c r="AQ2" s="59" t="s">
+        <v>9</v>
+      </c>
     </row>
-    <row r="3" spans="1:41" ht="7.5" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="3" spans="1:43" ht="7.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A3" s="16">
         <v>3</v>
       </c>
@@ -16241,8 +16261,14 @@
       <c r="AO3" s="59" t="s">
         <v>9</v>
       </c>
+      <c r="AP3" s="62" t="s">
+        <v>9</v>
+      </c>
+      <c r="AQ3" s="59" t="s">
+        <v>9</v>
+      </c>
     </row>
-    <row r="4" spans="1:41" ht="7.5" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="4" spans="1:43" ht="7.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A4" s="16">
         <v>4</v>
       </c>
@@ -16366,8 +16392,14 @@
       <c r="AO4" s="59" t="s">
         <v>9</v>
       </c>
+      <c r="AP4" s="62" t="s">
+        <v>9</v>
+      </c>
+      <c r="AQ4" s="59" t="s">
+        <v>9</v>
+      </c>
     </row>
-    <row r="5" spans="1:41" ht="7.5" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="5" spans="1:43" ht="7.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A5" s="16">
         <v>5</v>
       </c>
@@ -16492,8 +16524,14 @@
       <c r="AO5" s="59" t="s">
         <v>256</v>
       </c>
+      <c r="AP5" s="62" t="s">
+        <v>843</v>
+      </c>
+      <c r="AQ5" s="59" t="s">
+        <v>844</v>
+      </c>
     </row>
-    <row r="6" spans="1:41" ht="7.5" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="6" spans="1:43" ht="7.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A6" s="16">
         <v>6</v>
       </c>
@@ -16618,8 +16656,14 @@
       <c r="AO6" s="59" t="s">
         <v>256</v>
       </c>
+      <c r="AP6" s="62" t="s">
+        <v>843</v>
+      </c>
+      <c r="AQ6" s="59" t="s">
+        <v>844</v>
+      </c>
     </row>
-    <row r="7" spans="1:41" ht="7.5" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="7" spans="1:43" ht="7.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A7" s="16">
         <v>7</v>
       </c>
@@ -16744,8 +16788,14 @@
       <c r="AO7" s="59" t="s">
         <v>256</v>
       </c>
+      <c r="AP7" s="62" t="s">
+        <v>843</v>
+      </c>
+      <c r="AQ7" s="59" t="s">
+        <v>844</v>
+      </c>
     </row>
-    <row r="8" spans="1:41" ht="7.5" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="8" spans="1:43" ht="7.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A8" s="16">
         <v>8</v>
       </c>
@@ -16870,8 +16920,14 @@
       <c r="AO8" s="59" t="s">
         <v>256</v>
       </c>
+      <c r="AP8" s="62" t="s">
+        <v>843</v>
+      </c>
+      <c r="AQ8" s="59" t="s">
+        <v>844</v>
+      </c>
     </row>
-    <row r="9" spans="1:41" ht="7.5" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="9" spans="1:43" ht="7.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A9" s="16">
         <v>9</v>
       </c>
@@ -16996,8 +17052,14 @@
       <c r="AO9" s="59" t="s">
         <v>256</v>
       </c>
+      <c r="AP9" s="62" t="s">
+        <v>843</v>
+      </c>
+      <c r="AQ9" s="59" t="s">
+        <v>844</v>
+      </c>
     </row>
-    <row r="10" spans="1:41" ht="7.5" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="10" spans="1:43" ht="7.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A10" s="16">
         <v>10</v>
       </c>
@@ -17122,8 +17184,14 @@
       <c r="AO10" s="59" t="s">
         <v>256</v>
       </c>
+      <c r="AP10" s="62" t="s">
+        <v>843</v>
+      </c>
+      <c r="AQ10" s="59" t="s">
+        <v>844</v>
+      </c>
     </row>
-    <row r="11" spans="1:41" ht="7.5" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="11" spans="1:43" ht="7.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A11" s="16">
         <v>11</v>
       </c>
@@ -17248,8 +17316,14 @@
       <c r="AO11" s="59" t="s">
         <v>256</v>
       </c>
+      <c r="AP11" s="62" t="s">
+        <v>843</v>
+      </c>
+      <c r="AQ11" s="59" t="s">
+        <v>844</v>
+      </c>
     </row>
-    <row r="12" spans="1:41" ht="7.5" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="12" spans="1:43" ht="7.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A12" s="16">
         <v>12</v>
       </c>
@@ -17374,8 +17448,14 @@
       <c r="AO12" s="59" t="s">
         <v>256</v>
       </c>
+      <c r="AP12" s="62" t="s">
+        <v>843</v>
+      </c>
+      <c r="AQ12" s="59" t="s">
+        <v>844</v>
+      </c>
     </row>
-    <row r="13" spans="1:41" ht="7.5" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="13" spans="1:43" ht="7.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A13" s="16">
         <v>13</v>
       </c>
@@ -17500,8 +17580,14 @@
       <c r="AO13" s="59" t="s">
         <v>256</v>
       </c>
+      <c r="AP13" s="62" t="s">
+        <v>843</v>
+      </c>
+      <c r="AQ13" s="59" t="s">
+        <v>844</v>
+      </c>
     </row>
-    <row r="14" spans="1:41" ht="7.5" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="14" spans="1:43" ht="7.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A14" s="16">
         <v>14</v>
       </c>
@@ -17626,8 +17712,14 @@
       <c r="AO14" s="59" t="s">
         <v>256</v>
       </c>
+      <c r="AP14" s="62" t="s">
+        <v>843</v>
+      </c>
+      <c r="AQ14" s="59" t="s">
+        <v>844</v>
+      </c>
     </row>
-    <row r="15" spans="1:41" ht="7.5" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="15" spans="1:43" ht="7.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A15" s="16">
         <v>15</v>
       </c>
@@ -17752,8 +17844,14 @@
       <c r="AO15" s="59" t="s">
         <v>256</v>
       </c>
+      <c r="AP15" s="62" t="s">
+        <v>843</v>
+      </c>
+      <c r="AQ15" s="59" t="s">
+        <v>844</v>
+      </c>
     </row>
-    <row r="16" spans="1:41" ht="7.5" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="16" spans="1:43" ht="7.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A16" s="16">
         <v>16</v>
       </c>
@@ -17878,8 +17976,14 @@
       <c r="AO16" s="59" t="s">
         <v>256</v>
       </c>
+      <c r="AP16" s="62" t="s">
+        <v>843</v>
+      </c>
+      <c r="AQ16" s="59" t="s">
+        <v>844</v>
+      </c>
     </row>
-    <row r="17" spans="1:41" ht="7.5" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="17" spans="1:43" ht="7.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A17" s="16">
         <v>17</v>
       </c>
@@ -18004,8 +18108,14 @@
       <c r="AO17" s="59" t="s">
         <v>256</v>
       </c>
+      <c r="AP17" s="62" t="s">
+        <v>843</v>
+      </c>
+      <c r="AQ17" s="59" t="s">
+        <v>844</v>
+      </c>
     </row>
-    <row r="18" spans="1:41" ht="7.5" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="18" spans="1:43" ht="7.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A18" s="16">
         <v>18</v>
       </c>
@@ -18130,8 +18240,14 @@
       <c r="AO18" s="59" t="s">
         <v>256</v>
       </c>
+      <c r="AP18" s="62" t="s">
+        <v>843</v>
+      </c>
+      <c r="AQ18" s="59" t="s">
+        <v>844</v>
+      </c>
     </row>
-    <row r="19" spans="1:41" ht="7.5" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="19" spans="1:43" ht="7.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A19" s="16">
         <v>19</v>
       </c>
@@ -18256,8 +18372,14 @@
       <c r="AO19" s="59" t="s">
         <v>256</v>
       </c>
+      <c r="AP19" s="62" t="s">
+        <v>843</v>
+      </c>
+      <c r="AQ19" s="59" t="s">
+        <v>844</v>
+      </c>
     </row>
-    <row r="20" spans="1:41" ht="7.5" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="20" spans="1:43" ht="7.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A20" s="16">
         <v>20</v>
       </c>
@@ -18382,8 +18504,14 @@
       <c r="AO20" s="59" t="s">
         <v>256</v>
       </c>
+      <c r="AP20" s="62" t="s">
+        <v>843</v>
+      </c>
+      <c r="AQ20" s="59" t="s">
+        <v>844</v>
+      </c>
     </row>
-    <row r="21" spans="1:41" ht="7.5" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="21" spans="1:43" ht="7.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A21" s="16">
         <v>21</v>
       </c>
@@ -18508,8 +18636,14 @@
       <c r="AO21" s="59" t="s">
         <v>256</v>
       </c>
+      <c r="AP21" s="62" t="s">
+        <v>843</v>
+      </c>
+      <c r="AQ21" s="59" t="s">
+        <v>844</v>
+      </c>
     </row>
-    <row r="22" spans="1:41" ht="7.5" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="22" spans="1:43" ht="7.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A22" s="16">
         <v>22</v>
       </c>
@@ -18634,8 +18768,14 @@
       <c r="AO22" s="59" t="s">
         <v>256</v>
       </c>
+      <c r="AP22" s="62" t="s">
+        <v>843</v>
+      </c>
+      <c r="AQ22" s="59" t="s">
+        <v>844</v>
+      </c>
     </row>
-    <row r="23" spans="1:41" ht="7.5" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="23" spans="1:43" ht="7.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A23" s="16">
         <v>23</v>
       </c>
@@ -18760,8 +18900,14 @@
       <c r="AO23" s="59" t="s">
         <v>256</v>
       </c>
+      <c r="AP23" s="62" t="s">
+        <v>843</v>
+      </c>
+      <c r="AQ23" s="59" t="s">
+        <v>844</v>
+      </c>
     </row>
-    <row r="24" spans="1:41" ht="7.5" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="24" spans="1:43" ht="7.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A24" s="16">
         <v>24</v>
       </c>
@@ -18886,8 +19032,14 @@
       <c r="AO24" s="59" t="s">
         <v>256</v>
       </c>
+      <c r="AP24" s="62" t="s">
+        <v>843</v>
+      </c>
+      <c r="AQ24" s="59" t="s">
+        <v>844</v>
+      </c>
     </row>
-    <row r="25" spans="1:41" ht="7.5" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="25" spans="1:43" ht="7.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A25" s="16">
         <v>25</v>
       </c>
@@ -19012,8 +19164,14 @@
       <c r="AO25" s="59" t="s">
         <v>256</v>
       </c>
+      <c r="AP25" s="62" t="s">
+        <v>843</v>
+      </c>
+      <c r="AQ25" s="59" t="s">
+        <v>844</v>
+      </c>
     </row>
-    <row r="26" spans="1:41" ht="7.5" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="26" spans="1:43" ht="7.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A26" s="16">
         <v>26</v>
       </c>
@@ -19138,8 +19296,14 @@
       <c r="AO26" s="59" t="s">
         <v>256</v>
       </c>
+      <c r="AP26" s="62" t="s">
+        <v>843</v>
+      </c>
+      <c r="AQ26" s="59" t="s">
+        <v>844</v>
+      </c>
     </row>
-    <row r="27" spans="1:41" ht="7.5" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="27" spans="1:43" ht="7.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A27" s="16">
         <v>27</v>
       </c>
@@ -19264,8 +19428,14 @@
       <c r="AO27" s="59" t="s">
         <v>256</v>
       </c>
+      <c r="AP27" s="62" t="s">
+        <v>843</v>
+      </c>
+      <c r="AQ27" s="59" t="s">
+        <v>844</v>
+      </c>
     </row>
-    <row r="28" spans="1:41" ht="7.5" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="28" spans="1:43" ht="7.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A28" s="16">
         <v>28</v>
       </c>
@@ -19390,8 +19560,14 @@
       <c r="AO28" s="59" t="s">
         <v>256</v>
       </c>
+      <c r="AP28" s="62" t="s">
+        <v>843</v>
+      </c>
+      <c r="AQ28" s="59" t="s">
+        <v>844</v>
+      </c>
     </row>
-    <row r="29" spans="1:41" ht="7.5" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="29" spans="1:43" ht="7.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A29" s="16">
         <v>29</v>
       </c>
@@ -19516,8 +19692,14 @@
       <c r="AO29" s="59" t="s">
         <v>256</v>
       </c>
+      <c r="AP29" s="62" t="s">
+        <v>843</v>
+      </c>
+      <c r="AQ29" s="59" t="s">
+        <v>844</v>
+      </c>
     </row>
-    <row r="30" spans="1:41" ht="7.5" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="30" spans="1:43" ht="7.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A30" s="16">
         <v>30</v>
       </c>
@@ -19642,8 +19824,14 @@
       <c r="AO30" s="59" t="s">
         <v>256</v>
       </c>
+      <c r="AP30" s="62" t="s">
+        <v>843</v>
+      </c>
+      <c r="AQ30" s="59" t="s">
+        <v>844</v>
+      </c>
     </row>
-    <row r="31" spans="1:41" ht="7.5" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="31" spans="1:43" ht="7.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A31" s="16">
         <v>31</v>
       </c>
@@ -19768,8 +19956,14 @@
       <c r="AO31" s="59" t="s">
         <v>256</v>
       </c>
+      <c r="AP31" s="62" t="s">
+        <v>843</v>
+      </c>
+      <c r="AQ31" s="59" t="s">
+        <v>844</v>
+      </c>
     </row>
-    <row r="32" spans="1:41" ht="7.5" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="32" spans="1:43" ht="7.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A32" s="16">
         <v>32</v>
       </c>
@@ -19894,8 +20088,14 @@
       <c r="AO32" s="59" t="s">
         <v>256</v>
       </c>
+      <c r="AP32" s="62" t="s">
+        <v>843</v>
+      </c>
+      <c r="AQ32" s="59" t="s">
+        <v>844</v>
+      </c>
     </row>
-    <row r="33" spans="1:41" ht="7.5" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="33" spans="1:43" ht="7.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A33" s="16">
         <v>33</v>
       </c>
@@ -20020,8 +20220,14 @@
       <c r="AO33" s="59" t="s">
         <v>256</v>
       </c>
+      <c r="AP33" s="62" t="s">
+        <v>843</v>
+      </c>
+      <c r="AQ33" s="59" t="s">
+        <v>844</v>
+      </c>
     </row>
-    <row r="34" spans="1:41" ht="7.5" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="34" spans="1:43" ht="7.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A34" s="16">
         <v>34</v>
       </c>
@@ -20146,8 +20352,14 @@
       <c r="AO34" s="59" t="s">
         <v>255</v>
       </c>
+      <c r="AP34" s="62" t="s">
+        <v>843</v>
+      </c>
+      <c r="AQ34" s="59" t="s">
+        <v>844</v>
+      </c>
     </row>
-    <row r="35" spans="1:41" ht="7.5" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="35" spans="1:43" ht="7.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A35" s="16">
         <v>35</v>
       </c>
@@ -20272,8 +20484,14 @@
       <c r="AO35" s="59" t="s">
         <v>255</v>
       </c>
+      <c r="AP35" s="62" t="s">
+        <v>843</v>
+      </c>
+      <c r="AQ35" s="59" t="s">
+        <v>844</v>
+      </c>
     </row>
-    <row r="36" spans="1:41" ht="7.5" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="36" spans="1:43" ht="7.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A36" s="16">
         <v>36</v>
       </c>
@@ -20398,8 +20616,14 @@
       <c r="AO36" s="59" t="s">
         <v>255</v>
       </c>
+      <c r="AP36" s="62" t="s">
+        <v>843</v>
+      </c>
+      <c r="AQ36" s="59" t="s">
+        <v>844</v>
+      </c>
     </row>
-    <row r="37" spans="1:41" ht="7.5" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="37" spans="1:43" ht="7.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A37" s="16">
         <v>37</v>
       </c>
@@ -20524,8 +20748,14 @@
       <c r="AO37" s="59" t="s">
         <v>255</v>
       </c>
+      <c r="AP37" s="62" t="s">
+        <v>843</v>
+      </c>
+      <c r="AQ37" s="59" t="s">
+        <v>844</v>
+      </c>
     </row>
-    <row r="38" spans="1:41" ht="7.5" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="38" spans="1:43" ht="7.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A38" s="16">
         <v>38</v>
       </c>
@@ -20650,8 +20880,14 @@
       <c r="AO38" s="59" t="s">
         <v>255</v>
       </c>
+      <c r="AP38" s="62" t="s">
+        <v>843</v>
+      </c>
+      <c r="AQ38" s="59" t="s">
+        <v>844</v>
+      </c>
     </row>
-    <row r="39" spans="1:41" ht="7.5" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="39" spans="1:43" ht="7.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A39" s="16">
         <v>39</v>
       </c>
@@ -20776,8 +21012,14 @@
       <c r="AO39" s="59" t="s">
         <v>255</v>
       </c>
+      <c r="AP39" s="62" t="s">
+        <v>843</v>
+      </c>
+      <c r="AQ39" s="59" t="s">
+        <v>844</v>
+      </c>
     </row>
-    <row r="40" spans="1:41" ht="7.5" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="40" spans="1:43" ht="7.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A40" s="16">
         <v>40</v>
       </c>
@@ -20902,8 +21144,14 @@
       <c r="AO40" s="59" t="s">
         <v>255</v>
       </c>
+      <c r="AP40" s="62" t="s">
+        <v>843</v>
+      </c>
+      <c r="AQ40" s="59" t="s">
+        <v>844</v>
+      </c>
     </row>
-    <row r="41" spans="1:41" ht="7.5" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="41" spans="1:43" ht="7.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A41" s="16">
         <v>41</v>
       </c>
@@ -21028,8 +21276,14 @@
       <c r="AO41" s="59" t="s">
         <v>255</v>
       </c>
+      <c r="AP41" s="62" t="s">
+        <v>843</v>
+      </c>
+      <c r="AQ41" s="59" t="s">
+        <v>844</v>
+      </c>
     </row>
-    <row r="42" spans="1:41" ht="7.5" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="42" spans="1:43" ht="7.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A42" s="16">
         <v>42</v>
       </c>
@@ -21154,8 +21408,14 @@
       <c r="AO42" s="59" t="s">
         <v>255</v>
       </c>
+      <c r="AP42" s="62" t="s">
+        <v>843</v>
+      </c>
+      <c r="AQ42" s="59" t="s">
+        <v>844</v>
+      </c>
     </row>
-    <row r="43" spans="1:41" ht="7.5" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="43" spans="1:43" ht="7.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A43" s="16">
         <v>43</v>
       </c>
@@ -21280,8 +21540,14 @@
       <c r="AO43" s="59" t="s">
         <v>255</v>
       </c>
+      <c r="AP43" s="62" t="s">
+        <v>843</v>
+      </c>
+      <c r="AQ43" s="59" t="s">
+        <v>844</v>
+      </c>
     </row>
-    <row r="44" spans="1:41" ht="7.5" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="44" spans="1:43" ht="7.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A44" s="16">
         <v>44</v>
       </c>
@@ -21406,8 +21672,14 @@
       <c r="AO44" s="59" t="s">
         <v>255</v>
       </c>
+      <c r="AP44" s="62" t="s">
+        <v>843</v>
+      </c>
+      <c r="AQ44" s="59" t="s">
+        <v>844</v>
+      </c>
     </row>
-    <row r="45" spans="1:41" ht="7.5" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="45" spans="1:43" ht="7.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A45" s="16">
         <v>45</v>
       </c>
@@ -21532,8 +21804,14 @@
       <c r="AO45" s="59" t="s">
         <v>255</v>
       </c>
+      <c r="AP45" s="62" t="s">
+        <v>843</v>
+      </c>
+      <c r="AQ45" s="59" t="s">
+        <v>844</v>
+      </c>
     </row>
-    <row r="46" spans="1:41" ht="7.5" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="46" spans="1:43" ht="7.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A46" s="16">
         <v>46</v>
       </c>
@@ -21658,8 +21936,14 @@
       <c r="AO46" s="59" t="s">
         <v>255</v>
       </c>
+      <c r="AP46" s="62" t="s">
+        <v>843</v>
+      </c>
+      <c r="AQ46" s="59" t="s">
+        <v>844</v>
+      </c>
     </row>
-    <row r="47" spans="1:41" ht="7.5" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="47" spans="1:43" ht="7.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A47" s="16">
         <v>47</v>
       </c>
@@ -21784,8 +22068,14 @@
       <c r="AO47" s="59" t="s">
         <v>255</v>
       </c>
+      <c r="AP47" s="62" t="s">
+        <v>843</v>
+      </c>
+      <c r="AQ47" s="59" t="s">
+        <v>844</v>
+      </c>
     </row>
-    <row r="48" spans="1:41" ht="7.5" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="48" spans="1:43" ht="7.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A48" s="16">
         <v>48</v>
       </c>
@@ -21910,8 +22200,14 @@
       <c r="AO48" s="59" t="s">
         <v>255</v>
       </c>
+      <c r="AP48" s="62" t="s">
+        <v>843</v>
+      </c>
+      <c r="AQ48" s="59" t="s">
+        <v>844</v>
+      </c>
     </row>
-    <row r="49" spans="1:41" ht="7.5" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="49" spans="1:43" ht="7.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A49" s="16">
         <v>49</v>
       </c>
@@ -22036,8 +22332,14 @@
       <c r="AO49" s="59" t="s">
         <v>255</v>
       </c>
+      <c r="AP49" s="62" t="s">
+        <v>843</v>
+      </c>
+      <c r="AQ49" s="59" t="s">
+        <v>844</v>
+      </c>
     </row>
-    <row r="50" spans="1:41" ht="7.5" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="50" spans="1:43" ht="7.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A50" s="16">
         <v>50</v>
       </c>
@@ -22162,8 +22464,14 @@
       <c r="AO50" s="59" t="s">
         <v>255</v>
       </c>
+      <c r="AP50" s="62" t="s">
+        <v>843</v>
+      </c>
+      <c r="AQ50" s="59" t="s">
+        <v>844</v>
+      </c>
     </row>
-    <row r="51" spans="1:41" ht="7.5" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="51" spans="1:43" ht="7.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A51" s="16">
         <v>51</v>
       </c>
@@ -22288,8 +22596,14 @@
       <c r="AO51" s="59" t="s">
         <v>255</v>
       </c>
+      <c r="AP51" s="62" t="s">
+        <v>843</v>
+      </c>
+      <c r="AQ51" s="59" t="s">
+        <v>844</v>
+      </c>
     </row>
-    <row r="52" spans="1:41" ht="7.5" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="52" spans="1:43" ht="7.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A52" s="16">
         <v>52</v>
       </c>
@@ -22414,8 +22728,14 @@
       <c r="AO52" s="59" t="s">
         <v>255</v>
       </c>
+      <c r="AP52" s="62" t="s">
+        <v>843</v>
+      </c>
+      <c r="AQ52" s="59" t="s">
+        <v>844</v>
+      </c>
     </row>
-    <row r="53" spans="1:41" ht="7.5" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="53" spans="1:43" ht="7.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A53" s="16">
         <v>53</v>
       </c>
@@ -22540,8 +22860,14 @@
       <c r="AO53" s="59" t="s">
         <v>255</v>
       </c>
+      <c r="AP53" s="62" t="s">
+        <v>843</v>
+      </c>
+      <c r="AQ53" s="59" t="s">
+        <v>844</v>
+      </c>
     </row>
-    <row r="54" spans="1:41" ht="7.5" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="54" spans="1:43" ht="7.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A54" s="16">
         <v>54</v>
       </c>
@@ -22666,8 +22992,14 @@
       <c r="AO54" s="59" t="s">
         <v>255</v>
       </c>
+      <c r="AP54" s="62" t="s">
+        <v>843</v>
+      </c>
+      <c r="AQ54" s="59" t="s">
+        <v>844</v>
+      </c>
     </row>
-    <row r="55" spans="1:41" ht="7.5" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="55" spans="1:43" ht="7.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A55" s="16">
         <v>55</v>
       </c>
@@ -22792,8 +23124,14 @@
       <c r="AO55" s="59" t="s">
         <v>255</v>
       </c>
+      <c r="AP55" s="62" t="s">
+        <v>843</v>
+      </c>
+      <c r="AQ55" s="59" t="s">
+        <v>844</v>
+      </c>
     </row>
-    <row r="56" spans="1:41" ht="7.5" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="56" spans="1:43" ht="7.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A56" s="16">
         <v>56</v>
       </c>
@@ -22918,8 +23256,14 @@
       <c r="AO56" s="59" t="s">
         <v>255</v>
       </c>
+      <c r="AP56" s="62" t="s">
+        <v>843</v>
+      </c>
+      <c r="AQ56" s="59" t="s">
+        <v>844</v>
+      </c>
     </row>
-    <row r="57" spans="1:41" ht="7.5" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="57" spans="1:43" ht="7.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A57" s="16">
         <v>57</v>
       </c>
@@ -23044,8 +23388,14 @@
       <c r="AO57" s="59" t="s">
         <v>255</v>
       </c>
+      <c r="AP57" s="62" t="s">
+        <v>843</v>
+      </c>
+      <c r="AQ57" s="59" t="s">
+        <v>844</v>
+      </c>
     </row>
-    <row r="58" spans="1:41" ht="7.5" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="58" spans="1:43" ht="7.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A58" s="16">
         <v>58</v>
       </c>
@@ -23169,8 +23519,14 @@
       <c r="AO58" s="59" t="s">
         <v>528</v>
       </c>
+      <c r="AP58" s="62" t="s">
+        <v>843</v>
+      </c>
+      <c r="AQ58" s="59" t="s">
+        <v>844</v>
+      </c>
     </row>
-    <row r="59" spans="1:41" ht="7.5" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="59" spans="1:43" ht="7.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A59" s="16">
         <v>59</v>
       </c>
@@ -23294,8 +23650,14 @@
       <c r="AO59" s="59" t="s">
         <v>528</v>
       </c>
+      <c r="AP59" s="62" t="s">
+        <v>843</v>
+      </c>
+      <c r="AQ59" s="59" t="s">
+        <v>844</v>
+      </c>
     </row>
-    <row r="60" spans="1:41" ht="7.5" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="60" spans="1:43" ht="7.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A60" s="16">
         <v>60</v>
       </c>
@@ -23419,8 +23781,14 @@
       <c r="AO60" s="59" t="s">
         <v>528</v>
       </c>
+      <c r="AP60" s="62" t="s">
+        <v>843</v>
+      </c>
+      <c r="AQ60" s="59" t="s">
+        <v>844</v>
+      </c>
     </row>
-    <row r="61" spans="1:41" ht="7.5" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="61" spans="1:43" ht="7.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A61" s="16">
         <v>61</v>
       </c>
@@ -23543,6 +23911,12 @@
       </c>
       <c r="AO61" s="59" t="s">
         <v>528</v>
+      </c>
+      <c r="AP61" s="62" t="s">
+        <v>843</v>
+      </c>
+      <c r="AQ61" s="59" t="s">
+        <v>844</v>
       </c>
     </row>
   </sheetData>
